--- a/historical_data-Franklin_FTSE_China.xlsx
+++ b/historical_data-Franklin_FTSE_China.xlsx
@@ -1115,14 +1115,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="0%"/>
     <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="181" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="20">
+  <fonts count="36" x14ac:knownFonts="36">
     <font>
       <sz val="12.0"/>
       <name val="Droid Sans Fallback"/>
@@ -1130,6 +1131,111 @@
     </font>
     <font>
       <sz val="12.0"/>
+      <color rgb="FF9C0006"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF006100"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF9C6500"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Droid Sans Fallback"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Droid Sans Fallback"/>
       <charset val="134"/>
     </font>
@@ -1249,7 +1355,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="64">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1442,8 +1548,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC0DA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D79B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1A0C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BACC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1573,140 +1865,262 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFA7BFDE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="3" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="6" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="4" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="5" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="6" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="7" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="7" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="9" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="0" borderId="10" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="9" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="10" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="11" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="12" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="13" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="14" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="15" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="16" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="17" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="18" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="19" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="20" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="21" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="22" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="23" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="24" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="25" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="26" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="27" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="28" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="29" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="30" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="31" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="32" applyFill="1" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1724,7 +2138,142 @@
     <xf numFmtId="180" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" applyFont="1" fillId="33" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="34" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" applyFont="1" fillId="35" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="36" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" applyFont="1" fillId="37" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="0" borderId="13" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" applyFont="1" fillId="36" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" applyFont="1" fillId="38" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" applyFont="1" fillId="0" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" applyFont="1" fillId="0" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="0" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="40" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="41" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="42" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="43" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="44" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="45" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="46" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="47" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="48" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="49" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="50" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="51" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="52" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="53" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="54" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="55" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="56" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="57" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="58" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="59" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="60" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="61" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="62" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="63" applyFill="1" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1773,7 +2322,49 @@
       <xdr:spPr>
         <a:xfrm rot="0">
           <a:off x="5757266" y="0"/>
-          <a:ext cx="1134474" cy="2539961"/>
+          <a:ext cx="1134474" cy="2339938"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+        <a:noFill/>
+        <a:ln w="12700" cmpd="sng" cap="flat">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>197382</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>60323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>323309</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>12699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0">
+          <a:off x="5683699" y="2660609"/>
+          <a:ext cx="1497505" cy="3352749"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:noFill/>
@@ -1791,13 +2382,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G66"/>
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="8.0" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="8" width="8.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="0" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="16.499748" hidden="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1820,1489 +2414,1489 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A2" t="s" s="50">
+    <row r="2" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s" s="50">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s" s="50">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s" s="50">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="50">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s" s="50">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s" s="50">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A3" t="s" s="50">
+    <row r="3" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s" s="50">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s" s="50">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s" s="50">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s" s="50">
+      <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s" s="50">
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s" s="50">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A4" t="s" s="50">
+    <row r="4" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s" s="50">
+      <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s" s="50">
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s" s="50">
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s" s="50">
+      <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s" s="50">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s" s="50">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A5" t="s" s="50">
+    <row r="5" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s" s="50">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s" s="50">
+      <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s" s="50">
+      <c r="D5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" t="s" s="50">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s" s="50">
+      <c r="F5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s" s="50">
+      <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A6" t="s" s="50">
+    <row r="6" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s" s="50">
+      <c r="B6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s" s="50">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s" s="50">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s" s="50">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F6" t="s" s="50">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s" s="50">
+      <c r="G6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" t="s" s="50">
+    <row r="7" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s" s="50">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s" s="50">
+      <c r="C7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s" s="50">
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E7" t="s" s="50">
+      <c r="E7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s" s="50">
+      <c r="F7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G7" t="s" s="50">
+      <c r="G7" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" t="s" s="50">
+    <row r="8" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B8" t="s" s="50">
+      <c r="B8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C8" t="s" s="50">
+      <c r="C8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s" s="50">
+      <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="s" s="50">
+      <c r="E8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F8" t="s" s="50">
+      <c r="F8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G8" t="s" s="50">
+      <c r="G8" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" t="s" s="50">
+    <row r="9" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s" s="50">
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s" s="50">
+      <c r="C9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s" s="50">
+      <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E9" t="s" s="50">
+      <c r="E9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F9" t="s" s="50">
+      <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G9" t="s" s="50">
+      <c r="G9" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A10" t="s" s="50">
+    <row r="10" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s" s="50">
+      <c r="B10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s" s="50">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s" s="50">
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E10" t="s" s="50">
+      <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F10" t="s" s="50">
+      <c r="F10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G10" t="s" s="50">
+      <c r="G10" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A11" t="s" s="50">
+    <row r="11" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B11" t="s" s="50">
+      <c r="B11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C11" t="s" s="50">
+      <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D11" t="s" s="50">
+      <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E11" t="s" s="50">
+      <c r="E11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F11" t="s" s="50">
+      <c r="F11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G11" t="s" s="50">
+      <c r="G11" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" t="s" s="50">
+    <row r="12" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B12" t="s" s="50">
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s" s="50">
+      <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D12" t="s" s="50">
+      <c r="D12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s" s="50">
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F12" t="s" s="50">
+      <c r="F12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G12" t="s" s="50">
+      <c r="G12" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A13" t="s" s="50">
+    <row r="13" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B13" t="s" s="50">
+      <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C13" t="s" s="50">
+      <c r="C13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D13" t="s" s="50">
+      <c r="D13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E13" t="s" s="50">
+      <c r="E13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F13" t="s" s="50">
+      <c r="F13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G13" t="s" s="50">
+      <c r="G13" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" t="s" s="50">
+    <row r="14" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B14" t="s" s="50">
+      <c r="B14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C14" t="s" s="50">
+      <c r="C14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D14" t="s" s="50">
+      <c r="D14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E14" t="s" s="50">
+      <c r="E14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F14" t="s" s="50">
+      <c r="F14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G14" t="s" s="50">
+      <c r="G14" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" t="s" s="50">
+    <row r="15" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B15" t="s" s="50">
+      <c r="B15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C15" t="s" s="50">
+      <c r="C15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D15" t="s" s="50">
+      <c r="D15" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E15" t="s" s="50">
+      <c r="E15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F15" t="s" s="50">
+      <c r="F15" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G15" t="s" s="50">
+      <c r="G15" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A16" t="s" s="50">
+    <row r="16" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B16" t="s" s="50">
+      <c r="B16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C16" t="s" s="50">
+      <c r="C16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D16" t="s" s="50">
+      <c r="D16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E16" t="s" s="50">
+      <c r="E16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F16" t="s" s="50">
+      <c r="F16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="50">
+      <c r="G16" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" t="s" s="50">
+    <row r="17" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B17" t="s" s="50">
+      <c r="B17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C17" t="s" s="50">
+      <c r="C17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D17" t="s" s="50">
+      <c r="D17" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E17" t="s" s="50">
+      <c r="E17" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F17" t="s" s="50">
+      <c r="F17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G17" t="s" s="50">
+      <c r="G17" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" t="s" s="50">
+    <row r="18" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B18" t="s" s="50">
+      <c r="B18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C18" t="s" s="50">
+      <c r="C18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D18" t="s" s="50">
+      <c r="D18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E18" t="s" s="50">
+      <c r="E18" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F18" t="s" s="50">
+      <c r="F18" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G18" t="s" s="50">
+      <c r="G18" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" t="s" s="50">
+    <row r="19" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B19" t="s" s="50">
+      <c r="B19" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C19" t="s" s="50">
+      <c r="C19" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D19" t="s" s="50">
+      <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E19" t="s" s="50">
+      <c r="E19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F19" t="s" s="50">
+      <c r="F19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G19" t="s" s="50">
+      <c r="G19" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" t="s" s="50">
+    <row r="20" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B20" t="s" s="50">
+      <c r="B20" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C20" t="s" s="50">
+      <c r="C20" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D20" t="s" s="50">
+      <c r="D20" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E20" t="s" s="50">
+      <c r="E20" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F20" t="s" s="50">
+      <c r="F20" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G20" t="s" s="50">
+      <c r="G20" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" t="s" s="50">
+    <row r="21" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B21" t="s" s="50">
+      <c r="B21" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C21" t="s" s="50">
+      <c r="C21" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D21" t="s" s="50">
+      <c r="D21" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s" s="50">
+      <c r="E21" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F21" t="s" s="50">
+      <c r="F21" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G21" t="s" s="50">
+      <c r="G21" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A22" t="s" s="50">
+    <row r="22" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B22" t="s" s="50">
+      <c r="B22" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C22" t="s" s="50">
+      <c r="C22" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D22" t="s" s="50">
+      <c r="D22" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E22" t="s" s="50">
+      <c r="E22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F22" t="s" s="50">
+      <c r="F22" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G22" t="s" s="50">
+      <c r="G22" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" t="s" s="50">
+    <row r="23" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B23" t="s" s="50">
+      <c r="B23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C23" t="s" s="50">
+      <c r="C23" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D23" t="s" s="50">
+      <c r="D23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E23" t="s" s="50">
+      <c r="E23" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F23" t="s" s="50">
+      <c r="F23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="G23" t="s" s="50">
+      <c r="G23" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" t="s" s="50">
+    <row r="24" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s" s="50">
+      <c r="B24" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C24" t="s" s="50">
+      <c r="C24" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D24" t="s" s="50">
+      <c r="D24" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E24" t="s" s="50">
+      <c r="E24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F24" t="s" s="50">
+      <c r="F24" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G24" t="s" s="50">
+      <c r="G24" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" t="s" s="50">
+    <row r="25" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B25" t="s" s="50">
+      <c r="B25" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C25" t="s" s="50">
+      <c r="C25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D25" t="s" s="50">
+      <c r="D25" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E25" t="s" s="50">
+      <c r="E25" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F25" t="s" s="50">
+      <c r="F25" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G25" t="s" s="50">
+      <c r="G25" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" t="s" s="50">
+    <row r="26" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B26" t="s" s="50">
+      <c r="B26" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C26" t="s" s="50">
+      <c r="C26" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D26" t="s" s="50">
+      <c r="D26" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E26" t="s" s="50">
+      <c r="E26" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F26" t="s" s="50">
+      <c r="F26" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="G26" t="s" s="50">
+      <c r="G26" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A27" t="s" s="50">
+    <row r="27" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B27" t="s" s="50">
+      <c r="B27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C27" t="s" s="50">
+      <c r="C27" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D27" t="s" s="50">
+      <c r="D27" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E27" t="s" s="50">
+      <c r="E27" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F27" t="s" s="50">
+      <c r="F27" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G27" t="s" s="50">
+      <c r="G27" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" t="s" s="50">
+    <row r="28" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B28" t="s" s="50">
+      <c r="B28" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C28" t="s" s="50">
+      <c r="C28" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D28" t="s" s="50">
+      <c r="D28" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E28" t="s" s="50">
+      <c r="E28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F28" t="s" s="50">
+      <c r="F28" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G28" t="s" s="50">
+      <c r="G28" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A29" t="s" s="50">
+    <row r="29" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B29" t="s" s="50">
+      <c r="B29" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C29" t="s" s="50">
+      <c r="C29" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D29" t="s" s="50">
+      <c r="D29" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E29" t="s" s="50">
+      <c r="E29" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F29" t="s" s="50">
+      <c r="F29" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G29" t="s" s="50">
+      <c r="G29" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A30" t="s" s="50">
+    <row r="30" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B30" t="s" s="50">
+      <c r="B30" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C30" t="s" s="50">
+      <c r="C30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D30" t="s" s="50">
+      <c r="D30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E30" t="s" s="50">
+      <c r="E30" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F30" t="s" s="50">
+      <c r="F30" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G30" t="s" s="50">
+      <c r="G30" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" t="s" s="50">
+    <row r="31" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B31" t="s" s="50">
+      <c r="B31" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C31" t="s" s="50">
+      <c r="C31" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D31" t="s" s="50">
+      <c r="D31" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E31" t="s" s="50">
+      <c r="E31" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F31" t="s" s="50">
+      <c r="F31" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="G31" t="s" s="50">
+      <c r="G31" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A32" t="s" s="50">
+    <row r="32" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B32" t="s" s="50">
+      <c r="B32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C32" t="s" s="50">
+      <c r="C32" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D32" t="s" s="50">
+      <c r="D32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E32" t="s" s="50">
+      <c r="E32" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F32" t="s" s="50">
+      <c r="F32" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G32" t="s" s="50">
+      <c r="G32" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A33" t="s" s="50">
+    <row r="33" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B33" t="s" s="50">
+      <c r="B33" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C33" t="s" s="50">
+      <c r="C33" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D33" t="s" s="50">
+      <c r="D33" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E33" t="s" s="50">
+      <c r="E33" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F33" t="s" s="50">
+      <c r="F33" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="G33" t="s" s="50">
+      <c r="G33" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A34" t="s" s="50">
+    <row r="34" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B34" t="s" s="50">
+      <c r="B34" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C34" t="s" s="50">
+      <c r="C34" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D34" t="s" s="50">
+      <c r="D34" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E34" t="s" s="50">
+      <c r="E34" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F34" t="s" s="50">
+      <c r="F34" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="G34" t="s" s="50">
+      <c r="G34" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A35" t="s" s="50">
+    <row r="35" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B35" t="s" s="50">
+      <c r="B35" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C35" t="s" s="50">
+      <c r="C35" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D35" t="s" s="50">
+      <c r="D35" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E35" t="s" s="50">
+      <c r="E35" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F35" t="s" s="50">
+      <c r="F35" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="G35" t="s" s="50">
+      <c r="G35" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A36" t="s" s="50">
+    <row r="36" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B36" t="s" s="50">
+      <c r="B36" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C36" t="s" s="50">
+      <c r="C36" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D36" t="s" s="50">
+      <c r="D36" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E36" t="s" s="50">
+      <c r="E36" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F36" t="s" s="50">
+      <c r="F36" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G36" t="s" s="50">
+      <c r="G36" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A37" t="s" s="50">
+    <row r="37" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B37" t="s" s="50">
+      <c r="B37" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C37" t="s" s="50">
+      <c r="C37" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D37" t="s" s="50">
+      <c r="D37" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E37" t="s" s="50">
+      <c r="E37" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F37" t="s" s="50">
+      <c r="F37" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G37" t="s" s="50">
+      <c r="G37" s="1" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A38" t="s" s="50">
+    <row r="38" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B38" t="s" s="50">
+      <c r="B38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C38" t="s" s="50">
+      <c r="C38" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D38" t="s" s="50">
+      <c r="D38" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E38" t="s" s="50">
+      <c r="E38" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F38" t="s" s="50">
+      <c r="F38" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G38" t="s" s="50">
+      <c r="G38" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A39" t="s" s="50">
+    <row r="39" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B39" t="s" s="50">
+      <c r="B39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C39" t="s" s="50">
+      <c r="C39" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D39" t="s" s="50">
+      <c r="D39" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E39" t="s" s="50">
+      <c r="E39" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F39" t="s" s="50">
+      <c r="F39" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G39" t="s" s="50">
+      <c r="G39" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A40" t="s" s="50">
+    <row r="40" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B40" t="s" s="50">
+      <c r="B40" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C40" t="s" s="50">
+      <c r="C40" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D40" t="s" s="50">
+      <c r="D40" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E40" t="s" s="50">
+      <c r="E40" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F40" t="s" s="50">
+      <c r="F40" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="G40" t="s" s="50">
+      <c r="G40" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41" t="s" s="50">
+    <row r="41" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B41" t="s" s="50">
+      <c r="B41" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C41" t="s" s="50">
+      <c r="C41" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D41" t="s" s="50">
+      <c r="D41" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E41" t="s" s="50">
+      <c r="E41" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="F41" t="s" s="50">
+      <c r="F41" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G41" t="s" s="50">
+      <c r="G41" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42" t="s" s="50">
+    <row r="42" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B42" t="s" s="50">
+      <c r="B42" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C42" t="s" s="50">
+      <c r="C42" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D42" t="s" s="50">
+      <c r="D42" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E42" t="s" s="50">
+      <c r="E42" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F42" t="s" s="50">
+      <c r="F42" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G42" t="s" s="50">
+      <c r="G42" s="1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A43" t="s" s="50">
+    <row r="43" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B43" t="s" s="50">
+      <c r="B43" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C43" t="s" s="50">
+      <c r="C43" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D43" t="s" s="50">
+      <c r="D43" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E43" t="s" s="50">
+      <c r="E43" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F43" t="s" s="50">
+      <c r="F43" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="G43" t="s" s="50">
+      <c r="G43" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44" t="s" s="50">
+    <row r="44" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B44" t="s" s="50">
+      <c r="B44" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C44" t="s" s="50">
+      <c r="C44" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D44" t="s" s="50">
+      <c r="D44" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E44" t="s" s="50">
+      <c r="E44" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F44" t="s" s="50">
+      <c r="F44" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G44" t="s" s="50">
+      <c r="G44" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A45" t="s" s="50">
+    <row r="45" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B45" t="s" s="50">
+      <c r="B45" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C45" t="s" s="50">
+      <c r="C45" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D45" t="s" s="50">
+      <c r="D45" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E45" t="s" s="50">
+      <c r="E45" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F45" t="s" s="50">
+      <c r="F45" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="G45" t="s" s="50">
+      <c r="G45" s="1" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46" t="s" s="50">
+    <row r="46" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B46" t="s" s="50">
+      <c r="B46" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C46" t="s" s="50">
+      <c r="C46" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D46" t="s" s="50">
+      <c r="D46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E46" t="s" s="50">
+      <c r="E46" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F46" t="s" s="50">
+      <c r="F46" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="G46" t="s" s="50">
+      <c r="G46" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47" t="s" s="50">
+    <row r="47" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B47" t="s" s="50">
+      <c r="B47" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C47" t="s" s="50">
+      <c r="C47" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D47" t="s" s="50">
+      <c r="D47" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E47" t="s" s="50">
+      <c r="E47" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F47" t="s" s="50">
+      <c r="F47" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G47" t="s" s="50">
+      <c r="G47" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A48" t="s" s="50">
+    <row r="48" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B48" t="s" s="50">
+      <c r="B48" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C48" t="s" s="50">
+      <c r="C48" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D48" t="s" s="50">
+      <c r="D48" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E48" t="s" s="50">
+      <c r="E48" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F48" t="s" s="50">
+      <c r="F48" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G48" t="s" s="50">
+      <c r="G48" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A49" t="s" s="50">
+    <row r="49" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B49" t="s" s="50">
+      <c r="B49" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C49" t="s" s="50">
+      <c r="C49" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D49" t="s" s="50">
+      <c r="D49" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E49" t="s" s="50">
+      <c r="E49" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F49" t="s" s="50">
+      <c r="F49" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G49" t="s" s="50">
+      <c r="G49" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50" t="s" s="50">
+    <row r="50" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B50" t="s" s="50">
+      <c r="B50" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C50" t="s" s="50">
+      <c r="C50" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D50" t="s" s="50">
+      <c r="D50" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E50" t="s" s="50">
+      <c r="E50" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F50" t="s" s="50">
+      <c r="F50" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="G50" t="s" s="50">
+      <c r="G50" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A51" t="s" s="50">
+    <row r="51" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B51" t="s" s="50">
+      <c r="B51" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C51" t="s" s="50">
+      <c r="C51" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D51" t="s" s="50">
+      <c r="D51" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E51" t="s" s="50">
+      <c r="E51" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F51" t="s" s="50">
+      <c r="F51" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G51" t="s" s="50">
+      <c r="G51" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A52" t="s" s="50">
+    <row r="52" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B52" t="s" s="50">
+      <c r="B52" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C52" t="s" s="50">
+      <c r="C52" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D52" t="s" s="50">
+      <c r="D52" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E52" t="s" s="50">
+      <c r="E52" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="F52" t="s" s="50">
+      <c r="F52" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="G52" t="s" s="50">
+      <c r="G52" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A53" t="s" s="50">
+    <row r="53" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B53" t="s" s="50">
+      <c r="B53" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C53" t="s" s="50">
+      <c r="C53" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D53" t="s" s="50">
+      <c r="D53" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E53" t="s" s="50">
+      <c r="E53" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F53" t="s" s="50">
+      <c r="F53" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="G53" t="s" s="50">
+      <c r="G53" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A54" t="s" s="50">
+    <row r="54" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B54" t="s" s="50">
+      <c r="B54" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C54" t="s" s="50">
+      <c r="C54" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D54" t="s" s="50">
+      <c r="D54" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E54" t="s" s="50">
+      <c r="E54" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F54" t="s" s="50">
+      <c r="F54" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="G54" t="s" s="50">
+      <c r="G54" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A55" t="s" s="50">
+    <row r="55" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B55" t="s" s="50">
+      <c r="B55" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C55" t="s" s="50">
+      <c r="C55" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D55" t="s" s="50">
+      <c r="D55" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E55" t="s" s="50">
+      <c r="E55" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F55" t="s" s="50">
+      <c r="F55" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="G55" t="s" s="50">
+      <c r="G55" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A56" t="s" s="50">
+    <row r="56" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B56" t="s" s="50">
+      <c r="B56" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C56" t="s" s="50">
+      <c r="C56" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D56" t="s" s="50">
+      <c r="D56" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E56" t="s" s="50">
+      <c r="E56" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="F56" t="s" s="50">
+      <c r="F56" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="G56" t="s" s="50">
+      <c r="G56" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A57" t="s" s="50">
+    <row r="57" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B57" t="s" s="50">
+      <c r="B57" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C57" t="s" s="50">
+      <c r="C57" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D57" t="s" s="50">
+      <c r="D57" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E57" t="s" s="50">
+      <c r="E57" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F57" t="s" s="50">
+      <c r="F57" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="G57" t="s" s="50">
+      <c r="G57" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A58" t="s" s="50">
+    <row r="58" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B58" t="s" s="50">
+      <c r="B58" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C58" t="s" s="50">
+      <c r="C58" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D58" t="s" s="50">
+      <c r="D58" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E58" t="s" s="50">
+      <c r="E58" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F58" t="s" s="50">
+      <c r="F58" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="G58" t="s" s="50">
+      <c r="G58" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A59" t="s" s="50">
+    <row r="59" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B59" t="s" s="50">
+      <c r="B59" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C59" t="s" s="50">
+      <c r="C59" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D59" t="s" s="50">
+      <c r="D59" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E59" t="s" s="50">
+      <c r="E59" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F59" t="s" s="50">
+      <c r="F59" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G59" t="s" s="50">
+      <c r="G59" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A60" t="s" s="50">
+    <row r="60" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B60" t="s" s="50">
+      <c r="B60" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C60" t="s" s="50">
+      <c r="C60" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D60" t="s" s="50">
+      <c r="D60" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E60" t="s" s="50">
+      <c r="E60" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F60" t="s" s="50">
+      <c r="F60" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="G60" t="s" s="50">
+      <c r="G60" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A61" t="s" s="50">
+    <row r="61" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B61" t="s" s="50">
+      <c r="B61" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C61" t="s" s="50">
+      <c r="C61" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D61" t="s" s="50">
+      <c r="D61" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E61" t="s" s="50">
+      <c r="E61" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F61" t="s" s="50">
+      <c r="F61" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="G61" t="s" s="50">
+      <c r="G61" s="1" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A62" t="s" s="50">
+    <row r="62" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B62" t="s" s="50">
+      <c r="B62" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C62" t="s" s="50">
+      <c r="C62" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D62" t="s" s="50">
+      <c r="D62" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E62" t="s" s="50">
+      <c r="E62" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F62" t="s" s="50">
+      <c r="F62" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="G62" t="s" s="50">
+      <c r="G62" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A63" t="s" s="50">
+    <row r="63" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B63" t="s" s="50">
+      <c r="B63" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C63" t="s" s="50">
+      <c r="C63" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D63" t="s" s="50">
+      <c r="D63" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E63" t="s" s="50">
+      <c r="E63" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F63" t="s" s="50">
+      <c r="F63" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="G63" t="s" s="50">
+      <c r="G63" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A64" t="s" s="50">
+    <row r="64" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B64" t="s" s="50">
+      <c r="B64" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C64" t="s" s="50">
+      <c r="C64" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D64" t="s" s="50">
+      <c r="D64" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E64" t="s" s="50">
+      <c r="E64" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F64" t="s" s="50">
+      <c r="F64" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="G64" t="s" s="50">
+      <c r="G64" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A65" t="s" s="50">
+    <row r="65" spans="1:7" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B65" t="s" s="50">
+      <c r="B65" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C65" t="s" s="50">
+      <c r="C65" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D65" t="s" s="50">
+      <c r="D65" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E65" t="s" s="50">
+      <c r="E65" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F65" t="s" s="50">
+      <c r="F65" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G65" t="s" s="50">
+      <c r="G65" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A66" t="s" s="50">
+    <row r="66" spans="1:4" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B66" t="s" s="50">
+      <c r="B66" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C66" t="s" s="50">
+      <c r="C66" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="D66" t="s" s="50">
+      <c r="D66" s="1" t="s">
         <v>365</v>
       </c>
     </row>
